--- a/템플릿/국가철도50억미만_템플릿.xlsx
+++ b/템플릿/국가철도50억미만_템플릿.xlsx
@@ -1554,9 +1554,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1602,18 +1599,12 @@
     <xf numFmtId="41" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="6" fillId="0" borderId="56" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1641,6 +1632,72 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="16" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1686,70 +1743,13 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2102,53 +2102,53 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="183">
+      <c r="D1" s="151">
         <v>2</v>
       </c>
-      <c r="E1" s="183"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="185"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="153"/>
       <c r="H1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="183">
+      <c r="I1" s="151">
         <f>D2</f>
         <v>0</v>
       </c>
-      <c r="J1" s="183"/>
+      <c r="J1" s="151"/>
       <c r="K1" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="188"/>
-      <c r="M1" s="188"/>
-      <c r="N1" s="189" t="s">
+      <c r="L1" s="154"/>
+      <c r="M1" s="154"/>
+      <c r="N1" s="155" t="s">
         <v>49</v>
       </c>
-      <c r="O1" s="190"/>
-      <c r="P1" s="190"/>
-      <c r="Q1" s="190"/>
-      <c r="R1" s="190"/>
-      <c r="S1" s="190"/>
-      <c r="T1" s="190"/>
-      <c r="U1" s="190"/>
-      <c r="V1" s="190"/>
-      <c r="W1" s="190"/>
-      <c r="X1" s="190"/>
-      <c r="Y1" s="190"/>
-      <c r="Z1" s="190"/>
-      <c r="AA1" s="190"/>
-      <c r="AB1" s="190"/>
-      <c r="AC1" s="134"/>
-      <c r="AD1" s="154" t="s">
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="156"/>
+      <c r="Y1" s="156"/>
+      <c r="Z1" s="156"/>
+      <c r="AA1" s="156"/>
+      <c r="AB1" s="156"/>
+      <c r="AC1" s="133"/>
+      <c r="AD1" s="173" t="s">
         <v>50</v>
       </c>
-      <c r="AE1" s="154"/>
-      <c r="AF1" s="154"/>
-      <c r="AG1" s="154"/>
-      <c r="AH1" s="154"/>
-      <c r="AI1" s="154"/>
-      <c r="AJ1" s="154"/>
-      <c r="AK1" s="154"/>
+      <c r="AE1" s="173"/>
+      <c r="AF1" s="173"/>
+      <c r="AG1" s="173"/>
+      <c r="AH1" s="173"/>
+      <c r="AI1" s="173"/>
+      <c r="AJ1" s="173"/>
+      <c r="AK1" s="173"/>
       <c r="AL1" s="80"/>
       <c r="AM1" s="80"/>
       <c r="AN1" s="80"/>
@@ -2166,18 +2166,18 @@
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="184"/>
-      <c r="G2" s="185"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="153"/>
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="186">
+      <c r="I2" s="171">
         <f>I1</f>
         <v>0</v>
       </c>
-      <c r="J2" s="186"/>
+      <c r="J2" s="171"/>
       <c r="K2" s="73" t="s">
         <v>11</v>
       </c>
@@ -2187,29 +2187,29 @@
       <c r="O2" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="187"/>
-      <c r="Q2" s="187"/>
-      <c r="R2" s="187"/>
-      <c r="S2" s="187"/>
+      <c r="P2" s="172"/>
+      <c r="Q2" s="172"/>
+      <c r="R2" s="172"/>
+      <c r="S2" s="172"/>
       <c r="T2" s="84"/>
-      <c r="U2" s="169"/>
-      <c r="V2" s="169"/>
-      <c r="W2" s="169"/>
-      <c r="X2" s="169"/>
-      <c r="Y2" s="169"/>
-      <c r="Z2" s="169"/>
+      <c r="U2" s="157"/>
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5"/>
       <c r="AC2" s="115"/>
-      <c r="AD2" s="155"/>
-      <c r="AE2" s="155"/>
-      <c r="AF2" s="155"/>
-      <c r="AG2" s="155"/>
-      <c r="AH2" s="155"/>
-      <c r="AI2" s="155"/>
-      <c r="AJ2" s="155"/>
-      <c r="AK2" s="155"/>
-      <c r="AL2" s="139"/>
+      <c r="AD2" s="174"/>
+      <c r="AE2" s="174"/>
+      <c r="AF2" s="174"/>
+      <c r="AG2" s="174"/>
+      <c r="AH2" s="174"/>
+      <c r="AI2" s="174"/>
+      <c r="AJ2" s="174"/>
+      <c r="AK2" s="174"/>
+      <c r="AL2" s="138"/>
       <c r="AM2" s="5"/>
       <c r="AN2" s="5"/>
       <c r="AO2" s="5"/>
@@ -2232,110 +2232,110 @@
       <c r="BB2" s="107"/>
     </row>
     <row r="3" spans="1:54" s="12" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A3" s="170" t="s">
+      <c r="A3" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="158" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="172" t="s">
+      <c r="C3" s="160" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="174"/>
-      <c r="G3" s="174"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="172" t="s">
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="160" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="176"/>
-      <c r="M3" s="177"/>
-      <c r="N3" s="178" t="s">
+      <c r="J3" s="161"/>
+      <c r="K3" s="161"/>
+      <c r="L3" s="164"/>
+      <c r="M3" s="165"/>
+      <c r="N3" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="180" t="s">
+      <c r="O3" s="168" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="172" t="s">
+      <c r="P3" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="173"/>
-      <c r="R3" s="173"/>
-      <c r="S3" s="173"/>
-      <c r="T3" s="173"/>
-      <c r="U3" s="182"/>
+      <c r="Q3" s="161"/>
+      <c r="R3" s="161"/>
+      <c r="S3" s="161"/>
+      <c r="T3" s="161"/>
+      <c r="U3" s="170"/>
       <c r="V3" s="11"/>
-      <c r="W3" s="172" t="s">
+      <c r="W3" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="X3" s="173"/>
-      <c r="Y3" s="173"/>
-      <c r="Z3" s="173"/>
-      <c r="AA3" s="173"/>
-      <c r="AB3" s="174"/>
-      <c r="AC3" s="153"/>
-      <c r="AD3" s="172" t="s">
+      <c r="X3" s="161"/>
+      <c r="Y3" s="161"/>
+      <c r="Z3" s="161"/>
+      <c r="AA3" s="161"/>
+      <c r="AB3" s="162"/>
+      <c r="AC3" s="150"/>
+      <c r="AD3" s="160" t="s">
         <v>20</v>
       </c>
-      <c r="AE3" s="173"/>
-      <c r="AF3" s="173"/>
-      <c r="AG3" s="173"/>
-      <c r="AH3" s="173"/>
-      <c r="AI3" s="173"/>
-      <c r="AJ3" s="182"/>
-      <c r="AK3" s="151" t="s">
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="161"/>
+      <c r="AG3" s="161"/>
+      <c r="AH3" s="161"/>
+      <c r="AI3" s="161"/>
+      <c r="AJ3" s="170"/>
+      <c r="AK3" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="AL3" s="152"/>
-      <c r="AM3" s="152"/>
-      <c r="AN3" s="152"/>
+      <c r="AL3" s="149"/>
+      <c r="AM3" s="149"/>
+      <c r="AN3" s="149"/>
       <c r="AO3" s="79"/>
-      <c r="AP3" s="159" t="s">
+      <c r="AP3" s="178" t="s">
         <v>22</v>
       </c>
-      <c r="AQ3" s="161" t="s">
+      <c r="AQ3" s="180" t="s">
         <v>23</v>
       </c>
-      <c r="AR3" s="163" t="s">
+      <c r="AR3" s="182" t="s">
         <v>24</v>
       </c>
-      <c r="AS3" s="165" t="s">
+      <c r="AS3" s="184" t="s">
         <v>25</v>
       </c>
-      <c r="AT3" s="167" t="s">
+      <c r="AT3" s="186" t="s">
         <v>26</v>
       </c>
-      <c r="AU3" s="157" t="s">
+      <c r="AU3" s="176" t="s">
         <v>27</v>
       </c>
-      <c r="AV3" s="156" t="s">
+      <c r="AV3" s="175" t="s">
         <v>28</v>
       </c>
-      <c r="AW3" s="156" t="s">
+      <c r="AW3" s="175" t="s">
         <v>29</v>
       </c>
-      <c r="AX3" s="156" t="s">
+      <c r="AX3" s="175" t="s">
         <v>30</v>
       </c>
-      <c r="AY3" s="156" t="s">
+      <c r="AY3" s="175" t="s">
         <v>31</v>
       </c>
-      <c r="AZ3" s="156" t="s">
+      <c r="AZ3" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="BA3" s="156" t="s">
+      <c r="BA3" s="175" t="s">
         <v>33</v>
       </c>
-      <c r="BB3" s="156" t="s">
+      <c r="BB3" s="175" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:54" s="12" customFormat="1" ht="39.75" customHeight="1" thickBot="1">
-      <c r="A4" s="171"/>
-      <c r="B4" s="171"/>
+      <c r="A4" s="159"/>
+      <c r="B4" s="159"/>
       <c r="C4" s="30" t="s">
         <v>6</v>
       </c>
@@ -2369,8 +2369,8 @@
       <c r="M4" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="179"/>
-      <c r="O4" s="181"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="169"/>
       <c r="P4" s="30" t="s">
         <v>6</v>
       </c>
@@ -2449,30 +2449,30 @@
       <c r="AO4" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="AP4" s="160"/>
-      <c r="AQ4" s="162"/>
-      <c r="AR4" s="164"/>
-      <c r="AS4" s="166"/>
-      <c r="AT4" s="168"/>
-      <c r="AU4" s="158"/>
-      <c r="AV4" s="156"/>
-      <c r="AW4" s="156"/>
-      <c r="AX4" s="156"/>
-      <c r="AY4" s="156"/>
-      <c r="AZ4" s="156"/>
-      <c r="BA4" s="156"/>
-      <c r="BB4" s="156"/>
+      <c r="AP4" s="179"/>
+      <c r="AQ4" s="181"/>
+      <c r="AR4" s="183"/>
+      <c r="AS4" s="185"/>
+      <c r="AT4" s="187"/>
+      <c r="AU4" s="177"/>
+      <c r="AV4" s="175"/>
+      <c r="AW4" s="175"/>
+      <c r="AX4" s="175"/>
+      <c r="AY4" s="175"/>
+      <c r="AZ4" s="175"/>
+      <c r="BA4" s="175"/>
+      <c r="BB4" s="175"/>
     </row>
     <row r="5" spans="1:54" s="12" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A5" s="122"/>
       <c r="B5" s="122"/>
       <c r="C5" s="120"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="132"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="127"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="131"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="126"/>
       <c r="J5" s="39"/>
       <c r="K5" s="17"/>
       <c r="L5" s="39"/>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="W5" s="113"/>
       <c r="X5" s="56"/>
-      <c r="Y5" s="148"/>
+      <c r="Y5" s="145"/>
       <c r="Z5" s="56"/>
       <c r="AA5" s="55"/>
       <c r="AB5" s="44" t="e">
@@ -2510,7 +2510,7 @@
         <f t="shared" ref="AC5:AC43" si="4">IF(AB5&gt;=10,10,AB5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD5" s="149"/>
+      <c r="AD5" s="146"/>
       <c r="AE5" s="82"/>
       <c r="AF5" s="82"/>
       <c r="AG5" s="43"/>
@@ -2552,18 +2552,14 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AU5" s="27"/>
-      <c r="AV5" s="104">
-        <v>8940300000</v>
-      </c>
-      <c r="AW5" s="104">
-        <v>1182800000</v>
-      </c>
+      <c r="AV5" s="104"/>
+      <c r="AW5" s="104"/>
       <c r="AX5" s="104"/>
       <c r="AY5" s="104"/>
       <c r="AZ5" s="105"/>
       <c r="BA5" s="105">
-        <f t="shared" ref="BA5:BA14" si="11">AV5+AW5+AX5+AY5+AZ5</f>
-        <v>10123100000</v>
+        <f t="shared" ref="BA5:BA53" si="11">AV5+AW5+AX5+AY5+AZ5</f>
+        <v>0</v>
       </c>
       <c r="BB5" s="106">
         <f t="shared" ref="BB5:BB53" si="12">(AV5*I5)+(AW5*J5)+(AX5*K5)+(AY5*L5)+(AZ5*M5)</f>
@@ -2573,13 +2569,13 @@
     <row r="6" spans="1:54" s="12" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A6" s="122"/>
       <c r="B6" s="122"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="127"/>
+      <c r="C6" s="131"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="128"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="126"/>
       <c r="J6" s="39"/>
       <c r="K6" s="39"/>
       <c r="L6" s="39"/>
@@ -2591,7 +2587,7 @@
       <c r="O6" s="19">
         <v>1</v>
       </c>
-      <c r="P6" s="138"/>
+      <c r="P6" s="137"/>
       <c r="Q6" s="43"/>
       <c r="R6" s="43"/>
       <c r="S6" s="43"/>
@@ -2605,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="69"/>
-      <c r="X6" s="140"/>
+      <c r="X6" s="139"/>
       <c r="Y6" s="56"/>
       <c r="Z6" s="56"/>
       <c r="AA6" s="55"/>
@@ -2659,18 +2655,14 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AU6" s="27"/>
-      <c r="AV6" s="104">
-        <v>14567000000</v>
-      </c>
-      <c r="AW6" s="104">
-        <v>1884200000</v>
-      </c>
+      <c r="AV6" s="104"/>
+      <c r="AW6" s="104"/>
       <c r="AX6" s="104"/>
       <c r="AY6" s="104"/>
       <c r="AZ6" s="105"/>
       <c r="BA6" s="105">
-        <f>AV6+AW6+AX6+AY6+AZ6</f>
-        <v>16451200000</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="BB6" s="106">
         <f t="shared" si="12"/>
@@ -2681,12 +2673,12 @@
       <c r="A7" s="38"/>
       <c r="B7" s="38"/>
       <c r="C7" s="120"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
       <c r="F7" s="124"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="133"/>
+      <c r="G7" s="188"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="132"/>
       <c r="J7" s="39"/>
       <c r="K7" s="17"/>
       <c r="L7" s="39"/>
@@ -2698,7 +2690,7 @@
       <c r="O7" s="47">
         <v>1</v>
       </c>
-      <c r="P7" s="136"/>
+      <c r="P7" s="135"/>
       <c r="Q7" s="43"/>
       <c r="R7" s="43"/>
       <c r="S7" s="43"/>
@@ -2724,7 +2716,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD7" s="150"/>
+      <c r="AD7" s="147"/>
       <c r="AE7" s="81"/>
       <c r="AF7" s="119"/>
       <c r="AG7" s="43"/>
@@ -2787,13 +2779,13 @@
     <row r="8" spans="1:54" s="12" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A8" s="38"/>
       <c r="B8" s="38"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="131"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
       <c r="F8" s="124"/>
-      <c r="G8" s="141"/>
-      <c r="H8" s="130"/>
-      <c r="I8" s="127"/>
+      <c r="G8" s="189"/>
+      <c r="H8" s="129"/>
+      <c r="I8" s="126"/>
       <c r="J8" s="39"/>
       <c r="K8" s="39"/>
       <c r="L8" s="39"/>
@@ -2809,7 +2801,7 @@
       <c r="Q8" s="43"/>
       <c r="R8" s="43"/>
       <c r="S8" s="43"/>
-      <c r="T8" s="142"/>
+      <c r="T8" s="140"/>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2821,7 +2813,7 @@
       <c r="W8" s="69"/>
       <c r="X8" s="72"/>
       <c r="Y8" s="63"/>
-      <c r="Z8" s="143"/>
+      <c r="Z8" s="141"/>
       <c r="AA8" s="109"/>
       <c r="AB8" s="44" t="e">
         <f t="shared" si="3"/>
@@ -2831,7 +2823,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD8" s="150"/>
+      <c r="AD8" s="147"/>
       <c r="AE8" s="81"/>
       <c r="AF8" s="119"/>
       <c r="AG8" s="43"/>
@@ -2896,11 +2888,11 @@
       <c r="B9" s="53"/>
       <c r="C9" s="121"/>
       <c r="D9" s="120"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="129"/>
-      <c r="G9" s="128"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="127"/>
       <c r="H9" s="52"/>
-      <c r="I9" s="127"/>
+      <c r="I9" s="126"/>
       <c r="J9" s="39"/>
       <c r="K9" s="39"/>
       <c r="L9" s="39"/>
@@ -2942,7 +2934,7 @@
       <c r="AE9" s="119"/>
       <c r="AF9" s="119"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="137"/>
+      <c r="AH9" s="136"/>
       <c r="AI9" s="47">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -2999,12 +2991,12 @@
       <c r="A10" s="53"/>
       <c r="B10" s="53"/>
       <c r="C10" s="120"/>
-      <c r="D10" s="132"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="128"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="127"/>
       <c r="H10" s="52"/>
-      <c r="I10" s="127"/>
+      <c r="I10" s="126"/>
       <c r="J10" s="39"/>
       <c r="K10" s="17"/>
       <c r="L10" s="39"/>
@@ -3044,7 +3036,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD10" s="149"/>
+      <c r="AD10" s="146"/>
       <c r="AE10" s="82"/>
       <c r="AF10" s="82"/>
       <c r="AG10" s="43"/>
@@ -3105,12 +3097,12 @@
       <c r="A11" s="38"/>
       <c r="B11" s="38"/>
       <c r="C11" s="120"/>
-      <c r="D11" s="132"/>
+      <c r="D11" s="131"/>
       <c r="E11" s="124"/>
       <c r="F11" s="124"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="188"/>
       <c r="H11" s="52"/>
-      <c r="I11" s="127"/>
+      <c r="I11" s="126"/>
       <c r="J11" s="39"/>
       <c r="K11" s="39"/>
       <c r="L11" s="39"/>
@@ -3208,13 +3200,13 @@
     <row r="12" spans="1:54" s="12" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A12" s="53"/>
       <c r="B12" s="53"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="132"/>
+      <c r="C12" s="128"/>
+      <c r="D12" s="131"/>
       <c r="E12" s="124"/>
       <c r="F12" s="124"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="127"/>
+      <c r="G12" s="188"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="126"/>
       <c r="J12" s="39"/>
       <c r="K12" s="39"/>
       <c r="L12" s="39"/>
@@ -3252,7 +3244,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD12" s="150"/>
+      <c r="AD12" s="147"/>
       <c r="AE12" s="81"/>
       <c r="AF12" s="82"/>
       <c r="AG12" s="43"/>
@@ -3312,13 +3304,13 @@
     <row r="13" spans="1:54" s="12" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A13" s="53"/>
       <c r="B13" s="53"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="132"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="131"/>
       <c r="E13" s="124"/>
-      <c r="F13" s="129"/>
-      <c r="G13" s="128"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="127"/>
       <c r="H13" s="52"/>
-      <c r="I13" s="127"/>
+      <c r="I13" s="126"/>
       <c r="J13" s="39"/>
       <c r="K13" s="17"/>
       <c r="L13" s="39"/>
@@ -3421,9 +3413,9 @@
       <c r="D14" s="124"/>
       <c r="E14" s="124"/>
       <c r="F14" s="124"/>
-      <c r="G14" s="76"/>
+      <c r="G14" s="188"/>
       <c r="H14" s="52"/>
-      <c r="I14" s="127"/>
+      <c r="I14" s="126"/>
       <c r="J14" s="39"/>
       <c r="K14" s="39"/>
       <c r="L14" s="39"/>
@@ -3461,7 +3453,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD14" s="149"/>
+      <c r="AD14" s="146"/>
       <c r="AE14" s="119"/>
       <c r="AF14" s="114"/>
       <c r="AG14" s="43"/>
@@ -3525,7 +3517,7 @@
       <c r="D15" s="124"/>
       <c r="E15" s="124"/>
       <c r="F15" s="124"/>
-      <c r="G15" s="76"/>
+      <c r="G15" s="188"/>
       <c r="H15" s="52"/>
       <c r="I15" s="112"/>
       <c r="J15" s="39"/>
@@ -3541,7 +3533,7 @@
       </c>
       <c r="P15" s="20"/>
       <c r="Q15" s="24"/>
-      <c r="R15" s="135"/>
+      <c r="R15" s="134"/>
       <c r="S15" s="24"/>
       <c r="T15" s="57"/>
       <c r="U15" s="25">
@@ -3567,7 +3559,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD15" s="149"/>
+      <c r="AD15" s="146"/>
       <c r="AE15" s="81"/>
       <c r="AF15" s="81"/>
       <c r="AG15" s="43"/>
@@ -3613,7 +3605,10 @@
       <c r="AX15" s="104"/>
       <c r="AY15" s="104"/>
       <c r="AZ15" s="105"/>
-      <c r="BA15" s="105"/>
+      <c r="BA15" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB15" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -3621,12 +3616,12 @@
     </row>
     <row r="16" spans="1:54" s="12" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="32"/>
+      <c r="B16" s="143"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="143"/>
       <c r="E16" s="124"/>
       <c r="F16" s="124"/>
-      <c r="G16" s="37"/>
+      <c r="G16" s="38"/>
       <c r="H16" s="52"/>
       <c r="I16" s="112"/>
       <c r="J16" s="39"/>
@@ -3714,7 +3709,10 @@
       <c r="AX16" s="104"/>
       <c r="AY16" s="104"/>
       <c r="AZ16" s="105"/>
-      <c r="BA16" s="105"/>
+      <c r="BA16" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB16" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -3722,12 +3720,12 @@
     </row>
     <row r="17" spans="1:54" s="12" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A17" s="32"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="144"/>
-      <c r="D17" s="32"/>
+      <c r="B17" s="143"/>
+      <c r="C17" s="190"/>
+      <c r="D17" s="143"/>
       <c r="E17" s="124"/>
       <c r="F17" s="124"/>
-      <c r="G17" s="37"/>
+      <c r="G17" s="38"/>
       <c r="H17" s="52"/>
       <c r="I17" s="46"/>
       <c r="J17" s="39"/>
@@ -3815,7 +3813,10 @@
       <c r="AX17" s="104"/>
       <c r="AY17" s="104"/>
       <c r="AZ17" s="105"/>
-      <c r="BA17" s="105"/>
+      <c r="BA17" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB17" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -3823,12 +3824,12 @@
     </row>
     <row r="18" spans="1:54" s="12" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A18" s="32"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="37"/>
+      <c r="B18" s="143"/>
+      <c r="C18" s="143"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="38"/>
       <c r="H18" s="52"/>
       <c r="I18" s="46"/>
       <c r="J18" s="39"/>
@@ -3842,7 +3843,7 @@
       <c r="O18" s="19">
         <v>1</v>
       </c>
-      <c r="P18" s="136"/>
+      <c r="P18" s="135"/>
       <c r="Q18" s="43"/>
       <c r="R18" s="43"/>
       <c r="S18" s="43"/>
@@ -3916,7 +3917,10 @@
       <c r="AX18" s="104"/>
       <c r="AY18" s="104"/>
       <c r="AZ18" s="105"/>
-      <c r="BA18" s="105"/>
+      <c r="BA18" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB18" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -3924,15 +3928,15 @@
     </row>
     <row r="19" spans="1:54" s="12" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A19" s="32"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="37"/>
+      <c r="B19" s="143"/>
+      <c r="C19" s="143"/>
+      <c r="D19" s="143"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="143"/>
+      <c r="G19" s="38"/>
       <c r="H19" s="52"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="145"/>
+      <c r="J19" s="142"/>
       <c r="K19" s="17"/>
       <c r="L19" s="39"/>
       <c r="M19" s="45"/>
@@ -3945,7 +3949,7 @@
       </c>
       <c r="P19" s="20"/>
       <c r="Q19" s="24"/>
-      <c r="R19" s="135"/>
+      <c r="R19" s="134"/>
       <c r="S19" s="24"/>
       <c r="T19" s="57"/>
       <c r="U19" s="44">
@@ -4017,7 +4021,10 @@
       <c r="AX19" s="104"/>
       <c r="AY19" s="104"/>
       <c r="AZ19" s="105"/>
-      <c r="BA19" s="105"/>
+      <c r="BA19" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB19" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -4029,8 +4036,8 @@
       <c r="C20" s="74"/>
       <c r="D20" s="74"/>
       <c r="E20" s="74"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="37"/>
+      <c r="F20" s="143"/>
+      <c r="G20" s="38"/>
       <c r="H20" s="52"/>
       <c r="I20" s="123"/>
       <c r="J20" s="17"/>
@@ -4118,7 +4125,10 @@
       <c r="AX20" s="104"/>
       <c r="AY20" s="104"/>
       <c r="AZ20" s="105"/>
-      <c r="BA20" s="105"/>
+      <c r="BA20" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB20" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -4130,8 +4140,8 @@
       <c r="C21" s="74"/>
       <c r="D21" s="74"/>
       <c r="E21" s="74"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="37"/>
+      <c r="F21" s="143"/>
+      <c r="G21" s="38"/>
       <c r="H21" s="52"/>
       <c r="I21" s="123"/>
       <c r="J21" s="17"/>
@@ -4219,7 +4229,10 @@
       <c r="AX21" s="104"/>
       <c r="AY21" s="104"/>
       <c r="AZ21" s="105"/>
-      <c r="BA21" s="105"/>
+      <c r="BA21" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB21" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -4320,7 +4333,10 @@
       <c r="AX22" s="104"/>
       <c r="AY22" s="104"/>
       <c r="AZ22" s="105"/>
-      <c r="BA22" s="105"/>
+      <c r="BA22" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB22" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -4332,8 +4348,8 @@
       <c r="C23" s="74"/>
       <c r="D23" s="74"/>
       <c r="E23" s="74"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="37"/>
+      <c r="F23" s="143"/>
+      <c r="G23" s="38"/>
       <c r="H23" s="52"/>
       <c r="I23" s="123"/>
       <c r="J23" s="17"/>
@@ -4349,7 +4365,7 @@
       </c>
       <c r="P23" s="20"/>
       <c r="Q23" s="78"/>
-      <c r="R23" s="135"/>
+      <c r="R23" s="134"/>
       <c r="S23" s="24"/>
       <c r="T23" s="57"/>
       <c r="U23" s="44">
@@ -4421,7 +4437,10 @@
       <c r="AX23" s="104"/>
       <c r="AY23" s="104"/>
       <c r="AZ23" s="105"/>
-      <c r="BA23" s="105"/>
+      <c r="BA23" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB23" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -4433,8 +4452,8 @@
       <c r="C24" s="74"/>
       <c r="D24" s="74"/>
       <c r="E24" s="74"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="37"/>
+      <c r="F24" s="143"/>
+      <c r="G24" s="38"/>
       <c r="H24" s="52"/>
       <c r="I24" s="123"/>
       <c r="J24" s="17"/>
@@ -4522,7 +4541,10 @@
       <c r="AX24" s="104"/>
       <c r="AY24" s="104"/>
       <c r="AZ24" s="105"/>
-      <c r="BA24" s="105"/>
+      <c r="BA24" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB24" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -4534,8 +4556,8 @@
       <c r="C25" s="74"/>
       <c r="D25" s="74"/>
       <c r="E25" s="74"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
       <c r="H25" s="52"/>
       <c r="I25" s="123"/>
       <c r="J25" s="17"/>
@@ -4623,7 +4645,10 @@
       <c r="AX25" s="104"/>
       <c r="AY25" s="104"/>
       <c r="AZ25" s="105"/>
-      <c r="BA25" s="105"/>
+      <c r="BA25" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB25" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -4635,8 +4660,8 @@
       <c r="C26" s="74"/>
       <c r="D26" s="74"/>
       <c r="E26" s="74"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
       <c r="H26" s="52"/>
       <c r="I26" s="123"/>
       <c r="J26" s="17"/>
@@ -4724,7 +4749,10 @@
       <c r="AX26" s="104"/>
       <c r="AY26" s="104"/>
       <c r="AZ26" s="105"/>
-      <c r="BA26" s="105"/>
+      <c r="BA26" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB26" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -4736,8 +4764,8 @@
       <c r="C27" s="74"/>
       <c r="D27" s="74"/>
       <c r="E27" s="74"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="37"/>
+      <c r="F27" s="143"/>
+      <c r="G27" s="38"/>
       <c r="H27" s="52"/>
       <c r="I27" s="123"/>
       <c r="J27" s="17"/>
@@ -4825,7 +4853,10 @@
       <c r="AX27" s="104"/>
       <c r="AY27" s="104"/>
       <c r="AZ27" s="105"/>
-      <c r="BA27" s="105"/>
+      <c r="BA27" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB27" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -4837,8 +4868,8 @@
       <c r="C28" s="74"/>
       <c r="D28" s="74"/>
       <c r="E28" s="74"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="37"/>
+      <c r="F28" s="143"/>
+      <c r="G28" s="38"/>
       <c r="H28" s="52"/>
       <c r="I28" s="123"/>
       <c r="J28" s="17"/>
@@ -4926,7 +4957,10 @@
       <c r="AX28" s="104"/>
       <c r="AY28" s="104"/>
       <c r="AZ28" s="105"/>
-      <c r="BA28" s="105"/>
+      <c r="BA28" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB28" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -4938,8 +4972,8 @@
       <c r="C29" s="74"/>
       <c r="D29" s="74"/>
       <c r="E29" s="74"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="37"/>
+      <c r="F29" s="143"/>
+      <c r="G29" s="38"/>
       <c r="H29" s="52"/>
       <c r="I29" s="123"/>
       <c r="J29" s="17"/>
@@ -5027,7 +5061,10 @@
       <c r="AX29" s="104"/>
       <c r="AY29" s="104"/>
       <c r="AZ29" s="105"/>
-      <c r="BA29" s="105"/>
+      <c r="BA29" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB29" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5040,7 +5077,7 @@
       <c r="D30" s="74"/>
       <c r="E30" s="74"/>
       <c r="F30" s="74"/>
-      <c r="G30" s="37"/>
+      <c r="G30" s="38"/>
       <c r="H30" s="52"/>
       <c r="I30" s="123"/>
       <c r="J30" s="17"/>
@@ -5128,7 +5165,10 @@
       <c r="AX30" s="104"/>
       <c r="AY30" s="104"/>
       <c r="AZ30" s="105"/>
-      <c r="BA30" s="105"/>
+      <c r="BA30" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB30" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5140,8 +5180,8 @@
       <c r="C31" s="74"/>
       <c r="D31" s="74"/>
       <c r="E31" s="74"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="37"/>
+      <c r="F31" s="143"/>
+      <c r="G31" s="38"/>
       <c r="H31" s="52"/>
       <c r="I31" s="123"/>
       <c r="J31" s="17"/>
@@ -5229,7 +5269,10 @@
       <c r="AX31" s="104"/>
       <c r="AY31" s="104"/>
       <c r="AZ31" s="105"/>
-      <c r="BA31" s="105"/>
+      <c r="BA31" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB31" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5241,8 +5284,8 @@
       <c r="C32" s="74"/>
       <c r="D32" s="74"/>
       <c r="E32" s="74"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="37"/>
+      <c r="F32" s="143"/>
+      <c r="G32" s="38"/>
       <c r="H32" s="52"/>
       <c r="I32" s="123"/>
       <c r="J32" s="17"/>
@@ -5328,7 +5371,10 @@
       <c r="AX32" s="104"/>
       <c r="AY32" s="104"/>
       <c r="AZ32" s="105"/>
-      <c r="BA32" s="105"/>
+      <c r="BA32" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB32" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5340,8 +5386,8 @@
       <c r="C33" s="74"/>
       <c r="D33" s="74"/>
       <c r="E33" s="74"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="37"/>
+      <c r="F33" s="143"/>
+      <c r="G33" s="38"/>
       <c r="H33" s="52"/>
       <c r="I33" s="123"/>
       <c r="J33" s="17"/>
@@ -5429,7 +5475,10 @@
       <c r="AX33" s="104"/>
       <c r="AY33" s="104"/>
       <c r="AZ33" s="105"/>
-      <c r="BA33" s="105"/>
+      <c r="BA33" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB33" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5441,8 +5490,8 @@
       <c r="C34" s="74"/>
       <c r="D34" s="74"/>
       <c r="E34" s="74"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="37"/>
+      <c r="F34" s="143"/>
+      <c r="G34" s="38"/>
       <c r="H34" s="52"/>
       <c r="I34" s="123"/>
       <c r="J34" s="17"/>
@@ -5530,7 +5579,10 @@
       <c r="AX34" s="104"/>
       <c r="AY34" s="104"/>
       <c r="AZ34" s="105"/>
-      <c r="BA34" s="105"/>
+      <c r="BA34" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB34" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5542,8 +5594,8 @@
       <c r="C35" s="74"/>
       <c r="D35" s="74"/>
       <c r="E35" s="74"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="37"/>
+      <c r="F35" s="143"/>
+      <c r="G35" s="38"/>
       <c r="H35" s="52"/>
       <c r="I35" s="123"/>
       <c r="J35" s="17"/>
@@ -5631,7 +5683,10 @@
       <c r="AX35" s="104"/>
       <c r="AY35" s="104"/>
       <c r="AZ35" s="105"/>
-      <c r="BA35" s="105"/>
+      <c r="BA35" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB35" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5643,8 +5698,8 @@
       <c r="C36" s="74"/>
       <c r="D36" s="74"/>
       <c r="E36" s="74"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="37"/>
+      <c r="F36" s="143"/>
+      <c r="G36" s="38"/>
       <c r="H36" s="52"/>
       <c r="I36" s="123"/>
       <c r="J36" s="17"/>
@@ -5721,7 +5776,10 @@
       <c r="AX36" s="104"/>
       <c r="AY36" s="104"/>
       <c r="AZ36" s="105"/>
-      <c r="BA36" s="105"/>
+      <c r="BA36" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB36" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5733,8 +5791,8 @@
       <c r="C37" s="74"/>
       <c r="D37" s="74"/>
       <c r="E37" s="74"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="37"/>
+      <c r="F37" s="143"/>
+      <c r="G37" s="38"/>
       <c r="H37" s="52"/>
       <c r="I37" s="123"/>
       <c r="J37" s="17"/>
@@ -5822,7 +5880,10 @@
       <c r="AX37" s="104"/>
       <c r="AY37" s="104"/>
       <c r="AZ37" s="105"/>
-      <c r="BA37" s="105"/>
+      <c r="BA37" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB37" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5835,7 +5896,7 @@
       <c r="D38" s="74"/>
       <c r="E38" s="74"/>
       <c r="F38" s="74"/>
-      <c r="G38" s="126"/>
+      <c r="G38" s="125"/>
       <c r="H38" s="52"/>
       <c r="I38" s="123"/>
       <c r="J38" s="17"/>
@@ -5923,7 +5984,10 @@
       <c r="AX38" s="104"/>
       <c r="AY38" s="104"/>
       <c r="AZ38" s="105"/>
-      <c r="BA38" s="105"/>
+      <c r="BA38" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB38" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5935,8 +5999,8 @@
       <c r="C39" s="74"/>
       <c r="D39" s="74"/>
       <c r="E39" s="74"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="37"/>
+      <c r="F39" s="143"/>
+      <c r="G39" s="38"/>
       <c r="H39" s="52"/>
       <c r="I39" s="123"/>
       <c r="J39" s="17"/>
@@ -6024,7 +6088,10 @@
       <c r="AX39" s="104"/>
       <c r="AY39" s="104"/>
       <c r="AZ39" s="105"/>
-      <c r="BA39" s="105"/>
+      <c r="BA39" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB39" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6036,8 +6103,8 @@
       <c r="C40" s="74"/>
       <c r="D40" s="74"/>
       <c r="E40" s="74"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="37"/>
+      <c r="F40" s="143"/>
+      <c r="G40" s="38"/>
       <c r="H40" s="52"/>
       <c r="I40" s="123"/>
       <c r="J40" s="17"/>
@@ -6114,7 +6181,10 @@
       <c r="AX40" s="104"/>
       <c r="AY40" s="104"/>
       <c r="AZ40" s="105"/>
-      <c r="BA40" s="105"/>
+      <c r="BA40" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB40" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6126,8 +6196,8 @@
       <c r="C41" s="74"/>
       <c r="D41" s="74"/>
       <c r="E41" s="74"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="37"/>
+      <c r="F41" s="143"/>
+      <c r="G41" s="38"/>
       <c r="H41" s="52"/>
       <c r="I41" s="123"/>
       <c r="J41" s="17"/>
@@ -6215,7 +6285,10 @@
       <c r="AX41" s="104"/>
       <c r="AY41" s="104"/>
       <c r="AZ41" s="105"/>
-      <c r="BA41" s="105"/>
+      <c r="BA41" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB41" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6228,7 +6301,7 @@
       <c r="D42" s="74"/>
       <c r="E42" s="74"/>
       <c r="F42" s="74"/>
-      <c r="G42" s="37"/>
+      <c r="G42" s="38"/>
       <c r="H42" s="52"/>
       <c r="I42" s="123"/>
       <c r="J42" s="17"/>
@@ -6316,7 +6389,10 @@
       <c r="AX42" s="104"/>
       <c r="AY42" s="104"/>
       <c r="AZ42" s="105"/>
-      <c r="BA42" s="105"/>
+      <c r="BA42" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB42" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6328,8 +6404,8 @@
       <c r="C43" s="74"/>
       <c r="D43" s="74"/>
       <c r="E43" s="74"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="37"/>
+      <c r="F43" s="143"/>
+      <c r="G43" s="38"/>
       <c r="H43" s="52"/>
       <c r="I43" s="123"/>
       <c r="J43" s="17"/>
@@ -6417,7 +6493,10 @@
       <c r="AX43" s="104"/>
       <c r="AY43" s="104"/>
       <c r="AZ43" s="105"/>
-      <c r="BA43" s="105"/>
+      <c r="BA43" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB43" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6429,8 +6508,8 @@
       <c r="C44" s="74"/>
       <c r="D44" s="74"/>
       <c r="E44" s="74"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="37"/>
+      <c r="F44" s="143"/>
+      <c r="G44" s="38"/>
       <c r="H44" s="52"/>
       <c r="I44" s="123"/>
       <c r="J44" s="17"/>
@@ -6502,7 +6581,10 @@
       <c r="AX44" s="104"/>
       <c r="AY44" s="104"/>
       <c r="AZ44" s="105"/>
-      <c r="BA44" s="105"/>
+      <c r="BA44" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB44" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6514,8 +6596,8 @@
       <c r="C45" s="74"/>
       <c r="D45" s="74"/>
       <c r="E45" s="74"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="37"/>
+      <c r="F45" s="143"/>
+      <c r="G45" s="38"/>
       <c r="H45" s="52"/>
       <c r="I45" s="123"/>
       <c r="J45" s="17"/>
@@ -6603,7 +6685,10 @@
       <c r="AX45" s="104"/>
       <c r="AY45" s="104"/>
       <c r="AZ45" s="105"/>
-      <c r="BA45" s="105"/>
+      <c r="BA45" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB45" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6615,8 +6700,8 @@
       <c r="C46" s="74"/>
       <c r="D46" s="74"/>
       <c r="E46" s="74"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="37"/>
+      <c r="F46" s="143"/>
+      <c r="G46" s="38"/>
       <c r="H46" s="52"/>
       <c r="I46" s="123"/>
       <c r="J46" s="17"/>
@@ -6704,7 +6789,10 @@
       <c r="AX46" s="104"/>
       <c r="AY46" s="104"/>
       <c r="AZ46" s="105"/>
-      <c r="BA46" s="105"/>
+      <c r="BA46" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB46" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6716,8 +6804,8 @@
       <c r="C47" s="74"/>
       <c r="D47" s="74"/>
       <c r="E47" s="74"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="37"/>
+      <c r="F47" s="143"/>
+      <c r="G47" s="38"/>
       <c r="H47" s="52"/>
       <c r="I47" s="123"/>
       <c r="J47" s="17"/>
@@ -6805,7 +6893,10 @@
       <c r="AX47" s="104"/>
       <c r="AY47" s="104"/>
       <c r="AZ47" s="105"/>
-      <c r="BA47" s="105"/>
+      <c r="BA47" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB47" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6817,8 +6908,8 @@
       <c r="C48" s="74"/>
       <c r="D48" s="74"/>
       <c r="E48" s="74"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="37"/>
+      <c r="F48" s="143"/>
+      <c r="G48" s="38"/>
       <c r="H48" s="52"/>
       <c r="I48" s="123"/>
       <c r="J48" s="17"/>
@@ -6906,7 +6997,10 @@
       <c r="AX48" s="104"/>
       <c r="AY48" s="104"/>
       <c r="AZ48" s="105"/>
-      <c r="BA48" s="105"/>
+      <c r="BA48" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB48" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6918,8 +7012,8 @@
       <c r="C49" s="124"/>
       <c r="D49" s="124"/>
       <c r="E49" s="124"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="37"/>
+      <c r="F49" s="143"/>
+      <c r="G49" s="38"/>
       <c r="H49" s="52"/>
       <c r="I49" s="123"/>
       <c r="J49" s="17"/>
@@ -7007,7 +7101,10 @@
       <c r="AX49" s="104"/>
       <c r="AY49" s="104"/>
       <c r="AZ49" s="105"/>
-      <c r="BA49" s="105"/>
+      <c r="BA49" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB49" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -7018,9 +7115,9 @@
       <c r="B50" s="38"/>
       <c r="C50" s="124"/>
       <c r="D50" s="124"/>
-      <c r="E50" s="125"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="37"/>
+      <c r="E50" s="124"/>
+      <c r="F50" s="143"/>
+      <c r="G50" s="38"/>
       <c r="H50" s="52"/>
       <c r="I50" s="123"/>
       <c r="J50" s="17"/>
@@ -7108,7 +7205,10 @@
       <c r="AX50" s="104"/>
       <c r="AY50" s="104"/>
       <c r="AZ50" s="105"/>
-      <c r="BA50" s="105"/>
+      <c r="BA50" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB50" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -7120,8 +7220,8 @@
       <c r="C51" s="124"/>
       <c r="D51" s="124"/>
       <c r="E51" s="124"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="37"/>
+      <c r="F51" s="143"/>
+      <c r="G51" s="38"/>
       <c r="H51" s="52"/>
       <c r="I51" s="123"/>
       <c r="J51" s="17"/>
@@ -7209,7 +7309,10 @@
       <c r="AX51" s="104"/>
       <c r="AY51" s="104"/>
       <c r="AZ51" s="105"/>
-      <c r="BA51" s="105"/>
+      <c r="BA51" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB51" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -7221,8 +7324,8 @@
       <c r="C52" s="124"/>
       <c r="D52" s="124"/>
       <c r="E52" s="124"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="37"/>
+      <c r="F52" s="143"/>
+      <c r="G52" s="38"/>
       <c r="H52" s="52"/>
       <c r="I52" s="123"/>
       <c r="J52" s="17"/>
@@ -7310,7 +7413,10 @@
       <c r="AX52" s="104"/>
       <c r="AY52" s="104"/>
       <c r="AZ52" s="105"/>
-      <c r="BA52" s="105"/>
+      <c r="BA52" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB52" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -7322,8 +7428,8 @@
       <c r="C53" s="124"/>
       <c r="D53" s="124"/>
       <c r="E53" s="124"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="37"/>
+      <c r="F53" s="143"/>
+      <c r="G53" s="38"/>
       <c r="H53" s="52"/>
       <c r="I53" s="123"/>
       <c r="J53" s="17"/>
@@ -7411,7 +7517,10 @@
       <c r="AX53" s="104"/>
       <c r="AY53" s="104"/>
       <c r="AZ53" s="105"/>
-      <c r="BA53" s="105"/>
+      <c r="BA53" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="BB53" s="106">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -7419,24 +7528,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="N1:AB1"/>
-    <mergeCell ref="U2:Z2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:U3"/>
-    <mergeCell ref="W3:AB3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="P2:S2"/>
     <mergeCell ref="AD1:AK2"/>
     <mergeCell ref="BB3:BB4"/>
     <mergeCell ref="AU3:AU4"/>
@@ -7452,6 +7543,24 @@
     <mergeCell ref="BA3:BA4"/>
     <mergeCell ref="AT3:AT4"/>
     <mergeCell ref="AD3:AJ3"/>
+    <mergeCell ref="U2:Z2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:U3"/>
+    <mergeCell ref="W3:AB3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:AB1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
